--- a/public/invoices/GS-PHONEBOX-001-V4.0.xlsx
+++ b/public/invoices/GS-PHONEBOX-001-V4.0.xlsx
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D62"/>
+  <dimension ref="B1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -685,10 +685,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="98" customHeight="1">
+    <row r="12" ht="126" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>V4.0 — value-engineered build of the V3.1 scope. Same activation, same booth, same dates, same yellow palette; trimmed where it doesn't affect the on-day moment. Right-sized packaging (100 units), single ceiling camera (Gymshark handles media internally), leaner consumables kit, standard warehouse hold (painted shell tolerates), and a focused project-management engagement (weekly producer cadence, async-first). Activation remains Friday, July 17, 2026 at Euclid Oval, Lincoln Road Mall (Saturday, July 18 held as a weather contingency).</t>
+          <t>V4.0 — value-engineered build of the V3.1 scope, landing under $90K net. Same activation, same booth, same dates, same yellow palette; trimmed where it doesn't affect the on-day moment. Packaging stays at 200 units and warehouse hold remains climate-controlled per Client direction. Cuts: focused project-management engagement (weekly cadence), single ceiling camera (Gymshark handles media internally), leaner consumables, simplified venue dressing, install crew without dedicated permit-window supervisor, selfie mounts removed (guests use phones in-hand), and the store wayfinding kit dropped (Bond St VM team handles in-store wayfinding). Activation remains Friday, July 17, 2026 at Euclid Oval, Lincoln Road Mall (Saturday, July 18 held as a weather contingency).</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
     <row r="24" ht="24" customHeight="1">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Phase 02  —  Interactive Tech (V4 — single camera)</t>
+          <t>Phase 02  —  Interactive Tech (V4 — single camera, mounts removed)</t>
         </is>
       </c>
     </row>
@@ -884,410 +884,380 @@
     <row r="28" ht="36" customHeight="1">
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Selfie &amp; Belfie Mobile Mounts (basic)</t>
+          <t>Thermal Voucher Printer &amp; Shelf Mount</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Two simple wall-mounted phone holders for guests' own phones; painted to match interior</t>
+          <t>Dual-speed thermal ticket printer, wrapped, redundant roll inventory, firmware</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="29" ht="36" customHeight="1">
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Thermal Voucher Printer &amp; Shelf Mount</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Dual-speed thermal ticket printer, wrapped, redundant roll inventory, firmware</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="n">
         <v>2800</v>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="10" t="inlineStr">
+    <row r="29" ht="22" customHeight="1">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>Subtotal — Interactive Tech</t>
         </is>
       </c>
-      <c r="D30" s="11" t="n">
-        <v>11800</v>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>Phase 03  —  Branding, Signage &amp; Consumables (V4 — right-sized)</t>
-        </is>
+      <c r="D29" s="11" t="n">
+        <v>11200</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>Phase 03  —  Branding, Signage &amp; Consumables (V4 — packaging held at 200 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Disclosure &amp; Wayfinding Signage</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Camera-disclosure sign, queue management decals, brand lockup callouts in yellow palette</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>950</v>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Disclosure &amp; Wayfinding Signage</t>
+          <t>Venue Dressing Kit (V4 — simplified)</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Camera-disclosure sign, queue management decals, brand lockup callouts in yellow palette</t>
+          <t>A-frame sidewalk signage + pavement decals for the Euclid Oval street activation, yellow palette. Dedicated branded stanchions removed; BID-supplied crowd-control stanchions used at no cost.</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="33" ht="36" customHeight="1">
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Venue Dressing Kit</t>
+          <t>Daily Consumables &amp; Spares Kit (V4 — leaner)</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Portable A-frame signage, branded stanchions, pavement decals for the Euclid Oval street activation, yellow palette</t>
+          <t>Voucher paper rolls, cleaning supplies, sanitisation wipes, yellow touch-up paint, vinyl repair, gaffer. Trimmed buffer vs V3.1 — adequate for a single-day window.</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>1750</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="34" ht="36" customHeight="1">
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Daily Consumables &amp; Spares Kit (V4 — leaner)</t>
+          <t>Custom Product Packaging — 200 units</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Voucher paper rolls, cleaning supplies, sanitisation wipes, yellow touch-up paint, vinyl repair, gaffer. Trimmed buffer vs V3.1 — adequate for a single-day window.</t>
+          <t>Yellow-palette product boxes, structural board, full-colour offset print, 300 × 200 × 70 mm, flat-packed for load-in. Held at 200 units per Client direction.</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Custom Product Packaging (V4 — 100 units)</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Yellow-palette product boxes, structural board, full-colour offset print, 300 × 200 × 70 mm, flat-packed for load-in. Right-sized to 100 units (V3.1 was 200) at the same per-unit cost.</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="n">
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="B36" s="10" t="inlineStr">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Subtotal — Branding, Signage &amp; Consumables</t>
         </is>
       </c>
-      <c r="D36" s="11" t="n">
-        <v>6600</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1">
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Phase 04a  —  The Activation (Euclid Oval, 11 AM–8 PM)</t>
-        </is>
+      <c r="D35" s="11" t="n">
+        <v>8250</v>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Phase 04a  —  The Activation (Euclid Oval, 11 AM–8 PM, V4 — install supervisor removed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Inbound Logistics &amp; Install (V4 — no dedicated supervisor)</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Truck, rigging hardware, 3-person install crew, 4–6 hr install window. Lead technician (covered in Phase 04 on-site line) takes the supervisor role at load-in instead of a dedicated supervisor.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>4800</v>
       </c>
     </row>
     <row r="38" ht="36" customHeight="1">
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Inbound Logistics &amp; Install</t>
+          <t>On-Site Technicians (Extended to 8 PM)</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Truck, rigging hardware, 3-person install crew, permit-window supervisor, 4–6 hr install window</t>
+          <t>Dedicated lead technician plus rotating second tech for rush windows and breaks, covering an extended 11 AM–8 PM operating window. Includes pre-open soundcheck and post-close shutdown.</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>5800</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="39" ht="36" customHeight="1">
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>On-Site Technicians (Extended to 8 PM)</t>
+          <t>Same-Day Strike &amp; Outbound Freight</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Dedicated lead technician plus rotating second tech for rush windows and breaks, covering an extended 11 AM–8 PM operating window. Includes pre-open soundcheck and post-close shutdown.</t>
+          <t>Complete de-installation, module breakdown, crated outbound freight within Euclid Oval's contracted strike window. Site walk-through with the Lincoln Road BID operations team.</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="40" ht="36" customHeight="1">
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>Same-Day Strike &amp; Outbound Freight</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>Complete de-installation, module breakdown, crated outbound freight within Euclid Oval's contracted strike window. Site walk-through with the Lincoln Road BID operations team.</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="n">
         <v>3300</v>
       </c>
     </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="B41" s="10" t="inlineStr">
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>Subtotal — The Activation (Euclid Oval)</t>
         </is>
       </c>
-      <c r="D41" s="11" t="n">
-        <v>12100</v>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>Phase 04b  —  Logistics + Local Install at NYC Retail (V4 — standard hold)</t>
-        </is>
+      <c r="D40" s="11" t="n">
+        <v>11100</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Phase 04b  —  Logistics + Local Install at NYC Retail (V4 — wayfinding kit removed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Climate-Controlled Warehouse Hold</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Secure climate-controlled storage at the AGV Miami NYC staging facility between Miami strike and NYC delivery. Held at climate spec per Client direction.</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>2400</v>
       </c>
     </row>
     <row r="43" ht="36" customHeight="1">
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Standard Warehouse Hold (V4 — painted shell)</t>
+          <t>Inter-City Freight (Climate-Controlled Truck)</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Secure storage at the AGV Miami NYC staging facility between Miami strike and NYC delivery. V4 drops the climate-controlled premium since the painted shell is transit-tolerant; standard ambient hold is sufficient.</t>
+          <t>Miami → AGV Miami NYC staging facility with real-time GPS tracking, two-driver rotation, handoff documentation</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>1400</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="44" ht="36" customHeight="1">
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Inter-City Freight (Climate-Controlled Truck)</t>
+          <t>Light Touchup After First Activation</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Miami → AGV Miami NYC staging facility with real-time GPS tracking, two-driver rotation, handoff documentation</t>
+          <t>Single light cosmetic touchup pass after the Miami activation: scuff/scratch repair, paint colour-match, lightbox edge cleanup, IVR/camera/printer functional re-test. Brief refurbish, not a full repaint.</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>5500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Light Touchup After First Activation</t>
+          <t>White-Glove Delivery to NYC Retail Location</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Single light cosmetic touchup pass after the Miami activation: scuff/scratch repair, paint colour-match, lightbox edge cleanup, IVR/camera/printer functional re-test. Brief refurbish, not a full repaint.</t>
+          <t>Climate-controlled final-mile delivery from AGV Miami NYC staging to the Client's nominated NYC retail address. Scheduled overnight or pre-open per store operations.</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="46" ht="36" customHeight="1">
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>White-Glove Delivery to NYC Retail Location</t>
+          <t>Retail-Environment Install Crew</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Climate-controlled final-mile delivery from AGV Miami NYC staging to the Client's nominated NYC retail address. Scheduled overnight or pre-open per store operations.</t>
+          <t>2-person retail-environment install crew with floor-protection, retail-grade hand-tool kit, store operations liaison. 4-hour install window scheduled to avoid trading hours.</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2000</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="47" ht="36" customHeight="1">
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Retail-Environment Install Crew</t>
+          <t>In-Store Fixture Setup</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>2-person retail-environment install crew with floor-protection, retail-grade hand-tool kit, store operations liaison. 4-hour install window scheduled to avoid trading hours.</t>
+          <t>Anchoring to retail-spec floor (no permanent penetration), electrical drop, IVR + camera + printer + lightbox bring-up, on-floor commissioning sign-off with the store manager.</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>In-Store Fixture Setup</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>Anchoring to retail-spec floor (no permanent penetration), electrical drop, IVR + camera + printer + lightbox bring-up, on-floor commissioning sign-off with the store manager.</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="n">
         <v>2100</v>
       </c>
     </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Store Wayfinding &amp; Footfall Driver Kit</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>Sidewalk A-frame outside the store entrance, branded window-vinyl tease pointing to the Phone Box installation inside, in-store directional decals, and a printed/social CTA pack.</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="50" ht="22" customHeight="1">
-      <c r="B50" s="10" t="inlineStr">
+    <row r="48" ht="22" customHeight="1">
+      <c r="B48" s="10" t="inlineStr">
         <is>
           <t>Subtotal — Logistics + NYC Retail Install</t>
         </is>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D48" s="11" t="n">
         <v>17300</v>
       </c>
     </row>
-    <row r="51" ht="24" customHeight="1">
-      <c r="B51" s="6" t="inlineStr">
+    <row r="49" ht="24" customHeight="1">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Phase 05  —  Project Management (V4 — focused engagement)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="B52" s="7" t="inlineStr">
+    <row r="50" ht="36" customHeight="1">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Project Management Fee (V4 — leaner)</t>
         </is>
       </c>
-      <c r="C52" s="8" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>Dedicated senior producer, weekly status reporting (vs daily), milestone tracking, vendor / venue liaison, COI + insurance coordination, post-event reconciliation. Async-first cadence appropriate for a single-event programme; same producer, lighter touch than V3.1's $12K engagement.</t>
         </is>
       </c>
-      <c r="D52" s="9" t="n">
+      <c r="D50" s="9" t="n">
         <v>6000</v>
       </c>
     </row>
-    <row r="53" ht="22" customHeight="1">
-      <c r="B53" s="10" t="inlineStr">
+    <row r="51" ht="22" customHeight="1">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>Subtotal — Project Management</t>
         </is>
       </c>
-      <c r="D53" s="11" t="n">
+      <c r="D51" s="11" t="n">
         <v>6000</v>
       </c>
     </row>
-    <row r="55">
-      <c r="B55" s="12" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="12" t="inlineStr">
         <is>
           <t>Gross Production Investment</t>
         </is>
       </c>
-      <c r="D55" s="13" t="n">
-        <v>94350</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="14" t="inlineStr">
+      <c r="D53" s="13" t="n">
+        <v>94400</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="14" t="inlineStr">
         <is>
           <t>Less: Preferred Partner Credit</t>
         </is>
       </c>
-      <c r="D56" s="15" t="n">
+      <c r="D54" s="15" t="n">
         <v>-5000</v>
       </c>
     </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="B57" s="16" t="inlineStr">
+    <row r="55" ht="32" customHeight="1">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>NET V4.0 PRODUCTION INVESTMENT</t>
         </is>
       </c>
-      <c r="D57" s="17" t="n">
-        <v>89350</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="2" t="inlineStr">
+      <c r="D55" s="17" t="n">
+        <v>89400</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>PAYMENT TERMS</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="70" customHeight="1">
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>60% deposit ($53,610) due upon Client's written approval of this Scope of Work (Proposal execution). 40% balance ($35,740) due five (5) business days prior to first activation installation (on or before Friday, July 10, 2026). Payment exclusively via ACH electronic transfer or domestic wire transfer; ACH/wire details issued directly to the Client billing contact upon SoW approval. Reference GS-PHONEBOX-001 V4.0 on all remittances.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="32" customHeight="1">
-      <c r="B62" s="18" t="inlineStr">
-        <is>
-          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  jclarkson@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V4.0 — value-engineered, current proposed and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
+    <row r="58" ht="70" customHeight="1">
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>60% deposit ($53,640) due upon Client's written approval of this Scope of Work (Proposal execution). 40% balance ($35,760) due five (5) business days prior to first activation installation (on or before Friday, July 10, 2026). Payment exclusively via ACH electronic transfer or domestic wire transfer; ACH/wire details issued directly to the Client billing contact upon SoW approval. Reference GS-PHONEBOX-001 V4.0 on all remittances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="32" customHeight="1">
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  jclarkson@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V4.0 — value-engineered, current proposed (under $90K net) and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="22">
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="B54:C54"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B60:D60"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:D49"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B51:D51"/>
     <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B58:D58"/>
     <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B35:C35"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/invoices/GS-PHONEBOX-001-V4.0.xlsx
+++ b/public/invoices/GS-PHONEBOX-001-V4.0.xlsx
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D60"/>
+  <dimension ref="B1:D65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -688,14 +688,14 @@
     <row r="12" ht="126" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>V4.0 — value-engineered build of the V3.1 scope, landing under $90K net. Same activation, same booth, same dates, same yellow palette; trimmed where it doesn't affect the on-day moment. Packaging stays at 200 units and warehouse hold remains climate-controlled per Client direction. Cuts: focused project-management engagement (weekly cadence), single ceiling camera (Gymshark handles media internally), leaner consumables, simplified venue dressing, install crew without dedicated permit-window supervisor, selfie mounts removed (guests use phones in-hand), and the store wayfinding kit dropped (Bond St VM team handles in-store wayfinding). Activation remains Friday, July 17, 2026 at Euclid Oval, Lincoln Road Mall (Saturday, July 18 held as a weather contingency).</t>
+          <t>V4.0 — clarifications &amp; value-engineering on top of V3.1. Yellow palette confirmed; concealed motorised slot replaced with a true hinged back distribution door for staff operation from inside; walkie scaled to consumer-grade; ceiling camera held at single 4K (pending production-team review); basic static selfie/belfie wall mounts (articulating upgrade quoted as add-on); content capture omitted; disclosure &amp; wayfinding signage removed; venue dressing kit pared to stanchions only (qty TBC); store wayfinding kit removed; NYC base scope is transport-only with the local install team quoted as an available add-on. $5K Preferred Partner Credit retained. Activation: Friday, July 17, 2026, 11 AM–8 PM at Euclid Oval, Lincoln Road Mall (Saturday, July 18 held as a weather contingency).</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Phase 01  —  The Phone Box (Painted Yellow Finish)</t>
+          <t>Phase 01  —  The Phone Box (Painted Yellow, Hinged Back Door)</t>
         </is>
       </c>
     </row>
@@ -762,16 +762,16 @@
     <row r="19" ht="36" customHeight="1">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Concealed Sliding Prize Door</t>
+          <t>Hinged Back Distribution Door (V4 — replaces motorised slot)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Motorised, colour-matched, no visible handle on public face — for slot-style product handoff from the back-of-house staff compartment</t>
+          <t>True hinged back door, brand-yellow painted, no visible handle on the public face. Allows a Gymshark-supplied staff member to operate from inside the back-of-house compartment and hand product directly to the guest. Replaces the previously quoted concealed motorised sliding slot — simpler, lower-cost, and clearer staff workflow.</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>3400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1">
@@ -807,16 +807,16 @@
     <row r="22" ht="36" customHeight="1">
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Back-of-House Compartment + Back Access Door</t>
+          <t>Back-of-House Staff Compartment</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Interior partition wall + hinged back-access door + small staff stoop, allowing one Gymshark-supplied team member to occupy a private back compartment and dispense product through the motorised slot to the guest. Talent supplied by Client per the proposal exclusions.</t>
+          <t>Interior partition wall + small staff stoop creating a private back compartment behind the hinged distribution door (above). One Gymshark-supplied team member operates from inside, handing product through the back door. Talent supplied by Client per the proposal exclusions.</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>2400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1">
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>40550</v>
+        <v>38350</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Phase 02  —  Interactive Tech (V4 — single camera, mounts removed)</t>
+          <t>Phase 02  —  Interactive Tech (V4 — clarified specs)</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
     <row r="26" ht="36" customHeight="1">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Walkie-Talkie Pair (consumer-grade)</t>
+          <t>Walkie-Talkie Pair (V4 — consumer-grade)</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Off-the-shelf Motorola pair: one inside the booth for the guest, one with the on-site Gymshark athlete. Includes spares.</t>
+          <t>Off-the-shelf consumer Motorola pair: one inside the booth for the guest, one with the on-site Gymshark athlete; includes spare batteries. The originally-quoted line was a higher-tech encrypted relay with online live-call routing — scaled down here to a conventional radio per Client preference.</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
@@ -869,12 +869,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Ceiling Camera (V4 — single, value-engineered)</t>
+          <t>Single 4K Ceiling Camera (V4 — pending production review)</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Single 4K ceiling-mounted video+audio camera with cloud storage, live-preview monitoring, disclosure signage. Single camera is sufficient now that Gymshark handles media internally — V3.1 dual-camera coverage was redundant.</t>
+          <t>Single 4K ceiling-mounted video+audio camera with cloud storage and disclosure signage. Production team currently confirming compatibility and any further savings opportunity — this line may revise downward in a V4.1 once that review closes; price held as a placeholder.</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
@@ -884,59 +884,59 @@
     <row r="28" ht="36" customHeight="1">
       <c r="B28" s="7" t="inlineStr">
         <is>
+          <t>Selfie &amp; Belfie Wall Mounts (V4 — static basic)</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Two simple static wall-mounted phone holders for guests' own phones, painted to match the interior. Articulating selfie-stick belfie mount available as an upgrade ($900 instead of $400) — listed here as the V4 baseline.</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
           <t>Thermal Voucher Printer &amp; Shelf Mount</t>
         </is>
       </c>
-      <c r="C28" s="8" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Dual-speed thermal ticket printer, wrapped, redundant roll inventory, firmware</t>
         </is>
       </c>
-      <c r="D28" s="9" t="n">
+      <c r="D29" s="9" t="n">
         <v>2800</v>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="B29" s="10" t="inlineStr">
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>Subtotal — Interactive Tech</t>
         </is>
       </c>
-      <c r="D29" s="11" t="n">
-        <v>11200</v>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Phase 03  —  Branding, Signage &amp; Consumables (V4 — packaging held at 200 units)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Disclosure &amp; Wayfinding Signage</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Camera-disclosure sign, queue management decals, brand lockup callouts in yellow palette</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>950</v>
+      <c r="D30" s="11" t="n">
+        <v>11600</v>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Phase 03  —  Branding, Signage &amp; Consumables (V4 — disclosure removed, dressing pared)</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Venue Dressing Kit (V4 — simplified)</t>
+          <t>Venue Dressing Kit (V4 — stanchions only, qty TBC)</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>A-frame sidewalk signage + pavement decals for the Euclid Oval street activation, yellow palette. Dedicated branded stanchions removed; BID-supplied crowd-control stanchions used at no cost.</t>
+          <t>Branded stanchion poles + ropes for crowd management at the Euclid Oval street activation. Quantity / linear feet to be confirmed by Client; price held as a placeholder pending that confirmation.</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
@@ -946,12 +946,12 @@
     <row r="33" ht="36" customHeight="1">
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Daily Consumables &amp; Spares Kit (V4 — leaner)</t>
+          <t>Daily Consumables &amp; Spares Kit</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Voucher paper rolls, cleaning supplies, sanitisation wipes, yellow touch-up paint, vinyl repair, gaffer. Trimmed buffer vs V3.1 — adequate for a single-day window.</t>
+          <t>Voucher paper rolls, cleaning supplies, sanitisation wipes, yellow touch-up paint, vinyl repair, gaffer</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
@@ -980,25 +980,25 @@
         </is>
       </c>
       <c r="D35" s="11" t="n">
-        <v>8250</v>
+        <v>7300</v>
       </c>
     </row>
     <row r="36" ht="24" customHeight="1">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Phase 04a  —  The Activation (Euclid Oval, 11 AM–8 PM, V4 — install supervisor removed)</t>
+          <t>Phase 04a  —  The Activation (Euclid Oval, 11 AM–8 PM)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Inbound Logistics &amp; Install (V4 — no dedicated supervisor)</t>
+          <t>Inbound Logistics &amp; Install</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Truck, rigging hardware, 3-person install crew, 4–6 hr install window. Lead technician (covered in Phase 04 on-site line) takes the supervisor role at load-in instead of a dedicated supervisor.</t>
+          <t>Truck, rigging hardware, 3-person install crew, 4–6 hr install window. Lead technician takes the supervisor role at load-in.</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
@@ -1048,7 +1048,7 @@
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Phase 04b  —  Logistics + Local Install at NYC Retail (V4 — wayfinding kit removed)</t>
+          <t>Phase 04b  —  Logistics to NYC (V4 — Base, transport-only)</t>
         </is>
       </c>
     </row>
@@ -1085,12 +1085,12 @@
     <row r="44" ht="36" customHeight="1">
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Light Touchup After First Activation</t>
+          <t>Light Touchup at NYC Staging</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Single light cosmetic touchup pass after the Miami activation: scuff/scratch repair, paint colour-match, lightbox edge cleanup, IVR/camera/printer functional re-test. Brief refurbish, not a full repaint.</t>
+          <t>Light cosmetic touchup pass at AGV Miami's NYC shop after Miami strike, prior to flagship delivery. Per Client direction, the booth ships straight to the NY shop and is refreshed locally before final delivery to the flagship store — tightest possible timeline.</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
@@ -1100,162 +1100,192 @@
     <row r="45" ht="36" customHeight="1">
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>White-Glove Delivery to NYC Retail Location</t>
+          <t>White-Glove Delivery to Gymshark NYC Flagship</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Climate-controlled final-mile delivery from AGV Miami NYC staging to the Client's nominated NYC retail address. Scheduled overnight or pre-open per store operations.</t>
+          <t>Climate-controlled final-mile delivery from AGV Miami NYC staging to the Gymshark NYC flagship retail address. Scheduled overnight or pre-open per store operations.</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
         <v>2000</v>
       </c>
     </row>
-    <row r="46" ht="36" customHeight="1">
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Retail-Environment Install Crew</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>2-person retail-environment install crew with floor-protection, retail-grade hand-tool kit, store operations liaison. 4-hour install window scheduled to avoid trading hours.</t>
-        </is>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>2300</v>
-      </c>
-    </row>
-    <row r="47" ht="36" customHeight="1">
-      <c r="B47" s="7" t="inlineStr">
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Logistics to NYC (Base)</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>12900</v>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Phase 05  —  Project Management (V4 — lean engagement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Project Management Fee (V4 — lean)</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Dedicated senior producer, weekly status reporting (vs daily), milestone tracking, vendor / venue liaison, COI + insurance coordination, post-event reconciliation. Async-first cadence appropriate for a single-event programme.</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Project Management</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Gross Production Investment (Base)</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="n">
+        <v>87250</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Less: Preferred Partner Credit</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="n">
+        <v>-5000</v>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>NET V4.0 PRODUCTION INVESTMENT (BASE)</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="n">
+        <v>82250</v>
+      </c>
+    </row>
+    <row r="55" ht="24" customHeight="1">
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Optional Add-On  —  NYC Local Install Team (Available, Not in Base)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Local Install Team — 1 Lead + 2 Crew</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>On-site retail-environment install team for the Gymshark NYC flagship: 1 lead technician + 2 crew, floor-protection kit, retail-grade hand-tool kit, store-operations liaison. 4-hour install window scheduled to avoid trading hours.</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>In-Store Fixture Setup</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>Anchoring to retail-spec floor (no permanent penetration), electrical drop, IVR + camera + printer + lightbox bring-up, on-floor commissioning sign-off with the store manager.</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="n">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>Subtotal — Logistics + NYC Retail Install</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="n">
-        <v>17300</v>
-      </c>
-    </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>Phase 05  —  Project Management (V4 — focused engagement)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Project Management Fee (V4 — leaner)</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>Dedicated senior producer, weekly status reporting (vs daily), milestone tracking, vendor / venue liaison, COI + insurance coordination, post-event reconciliation. Async-first cadence appropriate for a single-event programme; same producer, lighter touch than V3.1's $12K engagement.</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="n">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="B51" s="10" t="inlineStr">
-        <is>
-          <t>Subtotal — Project Management</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="n">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="12" t="inlineStr">
-        <is>
-          <t>Gross Production Investment</t>
-        </is>
-      </c>
-      <c r="D53" s="13" t="n">
-        <v>94400</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="14" t="inlineStr">
-        <is>
-          <t>Less: Preferred Partner Credit</t>
-        </is>
-      </c>
-      <c r="D54" s="15" t="n">
-        <v>-5000</v>
-      </c>
-    </row>
-    <row r="55" ht="32" customHeight="1">
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>NET V4.0 PRODUCTION INVESTMENT</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="n">
-        <v>89400</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="2" t="inlineStr">
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Anchoring to retail-spec floor (no permanent penetration), electrical drop, IVR + camera + printer + lightbox bring-up, on-floor commissioning sign-off with the flagship store manager.</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>1600</v>
+      </c>
+    </row>
+    <row r="58" ht="22" customHeight="1">
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Optional Local Install Team</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="n">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="12" t="inlineStr">
+        <is>
+          <t>Net V4.0 with Optional Local Install Team</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="n">
+        <v>86650</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>PAYMENT TERMS</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="70" customHeight="1">
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>60% deposit ($53,640) due upon Client's written approval of this Scope of Work (Proposal execution). 40% balance ($35,760) due five (5) business days prior to first activation installation (on or before Friday, July 10, 2026). Payment exclusively via ACH electronic transfer or domestic wire transfer; ACH/wire details issued directly to the Client billing contact upon SoW approval. Reference GS-PHONEBOX-001 V4.0 on all remittances.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="32" customHeight="1">
-      <c r="B60" s="18" t="inlineStr">
-        <is>
-          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  jclarkson@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V4.0 — value-engineered, current proposed (under $90K net) and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
+    <row r="63" ht="70" customHeight="1">
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>60% deposit ($49,350) due upon Client's written approval of this Scope of Work (Proposal execution). 40% balance ($32,900) due five (5) business days prior to first activation installation (on or before Friday, July 10, 2026). Payment exclusively via ACH electronic transfer or domestic wire transfer; ACH/wire details issued directly to the Client billing contact upon SoW approval. Reference GS-PHONEBOX-001 V4.0 on all remittances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="32" customHeight="1">
+      <c r="B65" s="18" t="inlineStr">
+        <is>
+          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  jclarkson@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V4.0 — current proposed (Base under $90K; optional NYC install add-on still under $90K) and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="25">
     <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B54:C54"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B60:D60"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B52:C52"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B55:D55"/>
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B62:D62"/>
     <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B58:D58"/>
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B2:D2"/>

--- a/public/invoices/GS-PHONEBOX-001-V4.0.xlsx
+++ b/public/invoices/GS-PHONEBOX-001-V4.0.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4.0 — Value-Engineered" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V4.0 — Current Proposed" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V3.0 — Issued" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="V2.0 — Superseded" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -685,10 +687,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="126" customHeight="1">
+    <row r="12" ht="140" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>V4.0 — clarifications &amp; value-engineering on top of V3.1. Yellow palette confirmed; concealed motorised slot replaced with a true hinged back distribution door for staff operation from inside; walkie scaled to consumer-grade; ceiling camera held at single 4K (pending production-team review); basic static selfie/belfie wall mounts (articulating upgrade quoted as add-on); content capture omitted; disclosure &amp; wayfinding signage removed; venue dressing kit pared to stanchions only (qty TBC); store wayfinding kit removed; NYC base scope is transport-only with the local install team quoted as an available add-on. $5K Preferred Partner Credit retained. Activation: Friday, July 17, 2026, 11 AM–8 PM at Euclid Oval, Lincoln Road Mall (Saturday, July 18 held as a weather contingency).</t>
+          <t>V4.0 — Yellow palette confirmed; concealed motorised slot replaced with a true hinged back distribution door; tech package itemised against deck spec (2× Motorola RMU2040 radios, 2× Ring Mini Indoor cameras restored to dual per Ominto deck p.15, 80mm thermal voucher printer, 2× wall-mounted selfie stations); content capture omitted; disclosure &amp; wayfinding signage removed; venue dressing kit pared to stanchions only (qty TBC); 200-unit yellow-palette product packaging held; NYC base scope is transport-only with a local install team available as an add-on. $5K Preferred Partner Credit retained. Booth dimensions per Ominto V2 design: 164 × 94 × 213 cm body + 20 cm lightbox header. Activation: Friday, July 17, 2026, 11 AM–8 PM at Euclid Oval, Lincoln Road Mall (Saturday, July 18 held as a weather contingency).</t>
         </is>
       </c>
     </row>
@@ -707,7 +709,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Custom scenic fabrication, marine-grade paint in Miami yellow (PMS TBC by Ominto), two-piece modular construction</t>
+          <t>Custom scenic fabrication per Ominto V2 design pack. Footprint 164 × 94 cm (~5'4" × 3'1"); body height 213 cm (~7'0"); lightbox header +20 cm (total ≈7'8"). Two-piece modular construction (staff compartment 70 cm deep + guest compartment 94 cm deep). Marine-grade paint in Miami yellow (PMS TBC by Ominto).</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
@@ -722,7 +724,7 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>LED-backlit translucent face panels on all four sides; weatherproof housing</t>
+          <t>20 cm lightbox header on all four faces. LED-backlit translucent face panels with weatherproof housing, dimmable driver, single-cord power feed.</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
@@ -737,7 +739,7 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Tempered glass on front door + sides with custom-printed yellow-palette privacy vinyl</t>
+          <t>Tempered glass on front door + sides per Ominto deck spec. Custom-printed semi-transparent privacy vinyl preserves the reveal moment when guests enter; finish print-matched to yellow palette.</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
@@ -752,7 +754,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Four-wall matte paint finish in Miami yellow, dimensional bum mirror with scripted messaging</t>
+          <t>Four-wall matte paint finish in Miami yellow on interior compartment. Dimensional bum mirror with scripted messaging above and below. Interior compartment dim: 65 × 86 cm (back compartment) per Ominto V2 design.</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
@@ -782,7 +784,7 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Aluminium chequer-plate flooring, dome light, guest seat, branded analogue phone</t>
+          <t>Aluminium chequer-plate (five-bar pattern) flooring, circular dome overhead light, compact guest seat (~70 cm wide), and branded analogue phone with yellow handset. Shelf below the phone receives the thermal printer.</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
@@ -797,7 +799,7 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Wind-load, ballast plan, electrical schematics, CAD shop drawings, venue-compliance package</t>
+          <t>Wind-load, ballast plan, electrical schematics, CAD shop drawings, venue-compliance package. Reconciles deck V2 dimensions (164 × 94 × 213 cm + 20 cm lightbox) at engineering lock.</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
@@ -812,7 +814,7 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Interior partition wall + small staff stoop creating a private back compartment behind the hinged distribution door (above). One Gymshark-supplied team member operates from inside, handing product through the back door. Talent supplied by Client per the proposal exclusions.</t>
+          <t>70 cm-deep × 94 cm-wide private back compartment behind the hinged distribution door. Includes interior partition wall, small staff stoop, and dispensing shelf for product handoff. Talent supplied by Client per proposal exclusions.</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
@@ -832,7 +834,7 @@
     <row r="24" ht="24" customHeight="1">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Phase 02  —  Interactive Tech (V4 — clarified specs)</t>
+          <t>Phase 02  —  Interactive Tech (V4 — itemised hardware)</t>
         </is>
       </c>
     </row>
@@ -844,7 +846,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Multi-branch scripting, licensed voice talent, keypad mapping, redundant win/lose logic, QA</t>
+          <t>Multi-branch scripting, licensed voice talent, keypad mapping (* = YES, # = NO), redundant win/lose logic, QA. Wired to the analogue phone handset.</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
@@ -854,46 +856,46 @@
     <row r="26" ht="36" customHeight="1">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Walkie-Talkie Pair (V4 — consumer-grade)</t>
+          <t>Two-Way Radio Pair — Motorola RMU2040 (2 × $350)</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Off-the-shelf consumer Motorola pair: one inside the booth for the guest, one with the on-site Gymshark athlete; includes spare batteries. The originally-quoted line was a higher-tech encrypted relay with online live-call routing — scaled down here to a conventional radio per Client preference.</t>
+          <t>2 × Motorola RMU2040 RM-Series 2-Way Radios (2-channel, 2-watt UHF business-grade, license-free, ~250,000 sq ft / 12-floor range, NOAA weather alerts). One inside the booth for the guest, one with the on-site Gymshark athlete; includes spare batteries.</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Single 4K Ceiling Camera (V4 — pending production review)</t>
+          <t>Ceiling Cameras — Ring Mini Indoor Plug-In (2 × $150)</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Single 4K ceiling-mounted video+audio camera with cloud storage and disclosure signage. Production team currently confirming compatibility and any further savings opportunity — this line may revise downward in a V4.1 once that review closes; price held as a placeholder.</t>
+          <t>2 × Ring Mini Indoor Security Cameras (1080p HD, two-way talk, motion detection, plug-in / no batteries, Wi-Fi, white finish). Cloud storage via Ring Protect subscription. Ceiling-mounted in front and back compartments. Restored to dual-camera per the original Ominto deck spec (p.15).</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>2500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="28" ht="36" customHeight="1">
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Selfie &amp; Belfie Wall Mounts (V4 — static basic)</t>
+          <t>Wall-Mounted Selfie Stations (2 × $450)</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Two simple static wall-mounted phone holders for guests' own phones, painted to match the interior. Articulating selfie-stick belfie mount available as an upgrade ($900 instead of $400) — listed here as the V4 baseline.</t>
+          <t>2 × wall-mounted selfie stations, painted to match the booth interior — face-level + belfie-angle. Each station provides a stable phone holder for guests using their own devices. Replaces V3 mobile-phone-mount line.</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>400</v>
+        <v>900</v>
       </c>
     </row>
     <row r="29" ht="36" customHeight="1">
@@ -904,11 +906,11 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Dual-speed thermal ticket printer, wrapped, redundant roll inventory, firmware</t>
+          <t>80mm thermal ticket printer (Amazon-sourced, ~$1,500 hardware-equivalent class), shelf-mounted under the analogue phone, wrapped in yellow vinyl. Voucher template designed by Gymshark; AGV Miami handles printer procurement, firmware, redundant roll inventory.</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2800</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
@@ -918,7 +920,7 @@
         </is>
       </c>
       <c r="D30" s="11" t="n">
-        <v>11600</v>
+        <v>8900</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
@@ -1161,7 +1163,7 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>87250</v>
+        <v>84550</v>
       </c>
     </row>
     <row r="52">
@@ -1181,7 +1183,7 @@
         </is>
       </c>
       <c r="D53" s="17" t="n">
-        <v>82250</v>
+        <v>79550</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1">
@@ -1238,7 +1240,7 @@
         </is>
       </c>
       <c r="D60" s="13" t="n">
-        <v>86650</v>
+        <v>83950</v>
       </c>
     </row>
     <row r="62">
@@ -1251,14 +1253,14 @@
     <row r="63" ht="70" customHeight="1">
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>60% deposit ($49,350) due upon Client's written approval of this Scope of Work (Proposal execution). 40% balance ($32,900) due five (5) business days prior to first activation installation (on or before Friday, July 10, 2026). Payment exclusively via ACH electronic transfer or domestic wire transfer; ACH/wire details issued directly to the Client billing contact upon SoW approval. Reference GS-PHONEBOX-001 V4.0 on all remittances.</t>
+          <t>60% deposit ($47,730) due upon Client's written approval of this Scope of Work (Proposal execution). 40% balance ($31,820) due five (5) business days prior to first activation installation (on or before Friday, July 10, 2026). Payment exclusively via ACH electronic transfer or domestic wire transfer; ACH/wire details issued directly to the Client billing contact upon SoW approval. Reference GS-PHONEBOX-001 V4.0 on all remittances.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="32" customHeight="1">
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  jclarkson@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V4.0 — current proposed (Base under $90K; optional NYC install add-on still under $90K) and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
+          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  jclarkson@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V4.0 — current proposed (Base $79,550 net; with optional NYC install add-on $83,950 net) and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
         </is>
       </c>
     </row>
@@ -1292,4 +1294,1516 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D4AF37"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:D58"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>AGV MIAMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EXPERIENTIAL FABRICATION &amp; PRODUCTION  ·  PROPOSAL INVOICE  ·  Version 3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>PRODUCER</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>AGV Miami, LLC</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Gymshark Ltd.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>GS-PHONEBOX-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>1440 Church St</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Attn: Authorized Billing Contact</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Version 3.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Bohemia, NY 11716</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>c/o Ominto Studio</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Issue Date: April 29, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>jclarkson@agvmiami.com</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Activation: Friday, July 17, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>info@agoravisuals.com</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Venue: Euclid Oval, Lincoln Road Mall</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>3.0 SCOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Single-event programme: fully-painted pink British phone box with interactive call/voucher/photo tech, deployed for a one-day street activation at Euclid Oval, Lincoln Road Mall, Miami Beach on Friday, July 17, 2026 (Saturday, July 18 held as a weather contingency). Light touchup post-Miami; logistical return to NYC handoff destination — no NYC retail activation, no respray/rewrap package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Phase 01  —  The Phone Box (Painted Finish)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Phone Box Structural Shell</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Custom scenic fabrication, marine-grade paint in Gymshark Pink, two-piece modular construction</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>4-Sided Illuminated Lightbox Signage</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>LED-backlit translucent face panels on all four sides; weatherproof housing</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Glass &amp; Semi-Transparent Vinyl Panels</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Tempered glass on front door + sides with custom-printed semi-transparent privacy vinyl</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Painted Pink Interior (V3 — paint, not vinyl)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Four-wall matte paint finish (Gymshark Pink), dimensional bum mirror with scripted messaging. Replaces V2.0 vinyl lining for durability and finish quality.</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>3800</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Concealed Sliding Prize Door</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Motorised, colour-matched, no visible handle on public face</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Interior Finishes</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Aluminium chequer-plate flooring, dome light, guest seat, branded analogue phone</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Engineering, Structural Calcs &amp; Shop Drawings</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Wind-load, ballast plan, electrical schematics, CAD shop drawings, venue-compliance package</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — The Phone Box</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>38150</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Phase 02  —  Interactive Tech + Content Capture</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Pre-Recorded Call-Response (IVR) System</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Multi-branch scripting, licensed voice talent, keypad mapping, redundant win/lose logic, QA</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Live Call / Walkie-Talkie Relay</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Dual-mode encrypted relay, backup uplink, on-site producer headset, external broadcast</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Ceiling Dual Camera System</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Two 4K video+audio cameras, cloud storage, live-preview monitoring, disclosure signage</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Selfie &amp; Belfie Mobile Mounts</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Two pink wall-mounted holders with motion-triggered ring-light inserts, dual-height</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Thermal Voucher Printer &amp; Shelf Mount</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Dual-speed thermal ticket printer, pink wrap, redundant roll inventory, firmware</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Content Capture &amp; Media Handoff Platform</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Cloud workspace, colour-corrected proxies, organised file-naming, 48-hour handoff</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Interactive Tech + Content Capture</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Phase 03  —  Branding, Signage &amp; Consumables</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Disclosure &amp; Wayfinding Signage</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Camera-disclosure sign, queue management decals, brand lockup callouts in brand palette</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Venue Dressing Kit</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Portable A-frame signage, branded stanchions, pavement decals for the Euclid Oval street activation</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Daily Consumables &amp; Spares Kit</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Voucher paper rolls, cleaning supplies, sanitisation wipes, touch-up paint, vinyl repair, pink gaffer</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Branding, Signage &amp; Consumables</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Phase 04a  —  The Activation (Euclid Oval, Lincoln Road Mall, Miami Beach)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Inbound Logistics &amp; Install</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Truck, rigging hardware, 3-person install crew, permit-window supervisor, 4–6 hr install window</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>On-Site Technicians</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Dedicated lead technician plus rotating second tech for rush windows and breaks</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Same-Day Strike &amp; Outbound Freight</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Complete de-installation, module breakdown, crated outbound freight, full site restoration</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — The Activation (Euclid Oval)</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Phase 04b  —  Logistics to NYC (Asset Transfer Only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Climate-Controlled Warehouse Hold</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Secure climate-controlled storage at the AGV Miami NYC staging facility between Miami strike and NYC handoff</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Inter-City Freight (Climate-Controlled Truck)</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Miami → AGV Miami NYC staging facility with real-time GPS tracking, two-driver rotation, handoff documentation</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Light Touchup After First Activation (V3 — new line)</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Single light cosmetic touchup pass after Miami activation: scuff/scratch repair, paint colour-match, lightbox edge cleanup, IVR/camera/printer functional re-test</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Final Delivery to NYC Handoff Destination</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Climate-controlled final-mile delivery from AGV Miami NYC staging to client's designated NYC handoff address. Asset transfer only — no installation, commissioning, or activation.</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Logistics to NYC</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>12900</v>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>Phase 05  —  Project Management &amp; Client Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Project Management Fee</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Dedicated senior producer, weekly status reporting, milestone tracking, Change Order administration, vendor / venue liaison, COI + insurance coordination, post-event reconciliation</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Project Management</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="12" t="inlineStr">
+        <is>
+          <t>Gross Production Investment</t>
+        </is>
+      </c>
+      <c r="D51" s="13" t="n">
+        <v>100150</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="14" t="inlineStr">
+        <is>
+          <t>Less: Preferred Partner Credit</t>
+        </is>
+      </c>
+      <c r="D52" s="15" t="n">
+        <v>-5000</v>
+      </c>
+    </row>
+    <row r="53" ht="32" customHeight="1">
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>NET V3.0 PRODUCTION INVESTMENT</t>
+        </is>
+      </c>
+      <c r="D53" s="17" t="n">
+        <v>95150</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>PAYMENT TERMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="70" customHeight="1">
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>60% deposit ($57,090) due upon Client's written approval of this Scope of Work (Proposal execution). 40% balance ($38,060) due five (5) business days prior to first activation installation (on or before Friday, July 10, 2026). Payment exclusively via ACH electronic transfer or domestic wire transfer; ACH/wire details issued directly to the Client billing contact upon SoW approval. Reference GS-PHONEBOX-001 V3.0 on all remittances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  jclarkson@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V3.0 and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000C2A8"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:D69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="4" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>AGV MIAMI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EXPERIENTIAL FABRICATION &amp; PRODUCTION  ·  PROPOSAL INVOICE  ·  Version 2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>PRODUCER</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>CLIENT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>AGV Miami, LLC</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Gymshark Ltd.</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>GS-PHONEBOX-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>1440 Church St</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Attn: Authorized Billing Contact</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Version 2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Bohemia, NY 11716</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>c/o Ominto Studio</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Issue Date: April 29, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>jclarkson@agvmiami.com</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Event 01 (Miami): June 27, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>info@agoravisuals.com</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Event 02 (NYC Bond St): July 9 – Aug 6, 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2.0 SCOPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Two-event sequence. Event 01 — Miami: Lincoln Road Mall street activation on Saturday, June 27, 2026 (AGV Miami recommended Euclid Oval, 1100 block). Event 02 — New York: in-store fixture at Gymshark Bond St, delivered by July 9, 2026 to anchor the July 11 product launch and a 4-week in-store run through August 6, 2026. Inter-city respray/rewrap to NYC palette between events. [Superseded by V3.0 — included for reference only.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Phase 01  —  The Phone Box</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Phone Box Structural Shell</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Custom scenic fabrication, marine-grade paint, two-piece modular</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>4-Sided Illuminated Lightbox Signage</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>LED-backlit translucent face panels on all four sides</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Glass &amp; Semi-Transparent Vinyl Panels</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Tempered glass on front door + sides</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Pink Vinyl Interior Lining</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Four-wall pink vinyl wrap with 'bum mirror' messaging</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Concealed Sliding Prize Door</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Motorised, colour-matched</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Interior Finishes</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Chequer plate floor, dome light, seat, analogue phone</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Engineering, Structural Calcs &amp; Shop Drawings</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Wind-load, ballast, electrical, CAD</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — The Phone Box</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>37550</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Phase 02  —  Interactive Tech + Content Capture</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Pre-Recorded Call-Response (IVR) System</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Multi-branch scripting, licensed voice, QA</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Live Call / Walkie-Talkie Relay</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Dual-mode encrypted relay, backup uplink, producer headset</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Ceiling Dual Camera System</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Two 4K cameras, cloud storage, live-preview, disclosure signage</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Selfie &amp; Belfie Mobile Mounts</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Motion-triggered ring-light inserts, dual-height</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Thermal Voucher Printer &amp; Shelf Mount</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Dual-speed thermal printer, pink wrap, redundant roll inventory</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Content Capture &amp; Media Handoff Platform</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Cloud workspace, proxies, 48-hour handoff</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Interactive Tech + Content Capture</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>Phase 03  —  Branding, Signage &amp; Consumables</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Disclosure &amp; Wayfinding Signage</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Camera-disclosure, queue management decals, brand lockup callouts</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Venue Dressing Kit</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>A-frame signage, branded stanchions, pavement decals</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Daily Consumables &amp; Spares Kit</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Voucher rolls, cleaning, spares, gaffer</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Branding, Signage &amp; Consumables</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Phase 04a  —  Event 01: Miami Lincoln Road Street Activation</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Inbound Logistics &amp; Install (Miami)</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>3-person install crew, permit-window supervisor, 4–6 hr install window</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>On-Site Technicians (Miami)</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Lead technician + rotating second tech for rush windows</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Same-Day Strike &amp; Outbound Freight (Miami)</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>De-installation, module breakdown, crated outbound freight</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>3300</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Event 01 Miami</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>Phase 04b  —  Inter-City Respray/Rewrap to NYC Palette</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Climate-Controlled Warehouse Hold (~10 days)</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Secure climate-controlled storage between Miami strike and NYC respray</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>2900</v>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Inter-City Freight (Miami → NYC, Climate Truck)</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Dedicated climate truck with two-driver rotation, real-time GPS tracking, handoff documentation</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Exterior Respray to NYC Palette</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Sand &amp; prep, marine-grade respray to NYC product-launch colour callout, clear over-laminate</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>5400</v>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Interior Vinyl Refresh (NYC Product Launch Creative)</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Removal of Miami interior vinyl, application of NYC product-launch creative, mirror messaging update</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Lightbox Graphic Refresh (NYC Launch Creative)</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Reprint and reinstall four translucent lightbox faces with NYC launch wordmark and treatment</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Retail Compliance &amp; Store Re-Spec</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Anchoring/ballast for indoor floor, electrical recheck, fire-marshal review, COI re-issuance for Bond St</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Pre-Deployment QC &amp; Retail-Grade Certification</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Full reassembly inspection, IVR + camera + printer bench re-test, retail-grade finish certification</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Respray Package</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>24000</v>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>Phase 04c  —  Event 02: Gymshark Bond St Delivery &amp; 4-Week In-Store Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>White-Glove Delivery to Gymshark Bond St</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Climate-controlled delivery to 11 Bond St, NYC, scheduled overnight or pre-open. Target on or before July 9, 2026.</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Retail-Environment Install Crew</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>2-person crew with floor-protection, retail-grade hand-tool kit, store operations liaison, 4-hour install window</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>In-Store Fixture Setup</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Retail-spec floor anchoring, electrical drop, IVR + camera + printer + lightbox bring-up, on-floor sign-off with store manager</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>Store Wayfinding &amp; Footfall Driver Kit</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Sidewalk A-frame, branded window-vinyl tease, in-store directional decals, printed/social CTA pack</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>4-Week In-Store Presence Support</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Remote tech monitoring, weekly voucher-roll restock, content uploads, scenic touch-ups through August 6, 2026</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>Retail Strike &amp; Return Freight</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>End-of-launch de-installation, retail-grade floor restoration, return freight to Bohemia, NY facility</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="57" ht="22" customHeight="1">
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Event 02 Bond St</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>Phase 05  —  Project Management &amp; Client Services</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Project Management Fee</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Dedicated senior producer, weekly status, milestone tracking, COI + insurance coordination</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="10" t="inlineStr">
+        <is>
+          <t>Subtotal — Project Management</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Gross Production Investment</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="n">
+        <v>124150</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>Less: Preferred Partner Credit</t>
+        </is>
+      </c>
+      <c r="D63" s="15" t="n">
+        <v>-5000</v>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>NET V2.0 PRODUCTION INVESTMENT</t>
+        </is>
+      </c>
+      <c r="D64" s="17" t="n">
+        <v>119150</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>PAYMENT TERMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="70" customHeight="1">
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>60% deposit ($71,490) due upon Client's written approval of this Scope of Work (Proposal execution). 40% balance ($47,660) due five (5) business days prior to first activation installation (five (5) business days prior to Event 01 install). Payment exclusively via ACH electronic transfer or domestic wire transfer; ACH/wire details issued directly to the Client billing contact upon SoW approval. Reference GS-PHONEBOX-001 V2.0 on all remittances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="32" customHeight="1">
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  jclarkson@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V2.0 — superseded by V3.0 and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/public/invoices/GS-PHONEBOX-001-V4.0.xlsx
+++ b/public/invoices/GS-PHONEBOX-001-V4.0.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Venue: Euclid Oval, Lincoln Road Mall</t>
+          <t>Venue: Lincoln Road Mall</t>
         </is>
       </c>
     </row>
@@ -687,10 +687,10 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="140" customHeight="1">
+    <row r="12" ht="126" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>V4.0 — Yellow palette confirmed; concealed motorised slot replaced with a true hinged back distribution door; tech package itemised against deck spec (2× Motorola RMU2040 radios, 2× Ring Mini Indoor cameras restored to dual per Ominto deck p.15, 80mm thermal voucher printer, 2× wall-mounted selfie stations); content capture omitted; disclosure &amp; wayfinding signage removed; venue dressing kit pared to stanchions only (qty TBC); 200-unit yellow-palette product packaging held; NYC base scope is transport-only with a local install team available as an add-on. $5K Preferred Partner Credit retained. Booth dimensions per Ominto V2 design: 164 × 94 × 213 cm body + 20 cm lightbox header. Activation: Friday, July 17, 2026, 11 AM–8 PM at Euclid Oval, Lincoln Road Mall (Saturday, July 18 held as a weather contingency).</t>
+          <t>V4.0 — Yellow palette confirmed; concealed motorised slot replaced with a true hinged back distribution door; tech package itemised against deck spec (2× Motorola RMU2040 radios, 2× Ring Mini Indoor cameras restored to dual per Ominto deck p.15, 80mm thermal voucher printer, 2× wall-mounted selfie stations); content capture omitted; disclosure &amp; wayfinding signage removed; venue dressing kit pared to stanchions only (qty TBC); 200-unit yellow-palette product packaging held; NYC base scope is transport-only with a local install team available as an add-on. $5K Preferred Partner Credit retained. Booth dimensions per Ominto V2 design: 164 × 94 × 213 cm body + 20 cm lightbox header. Activation: Friday, July 17, 2026, 11 AM–8 PM at Lincoln Road Mall (Saturday, July 18 held as a weather contingency).</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Branded stanchion poles + ropes for crowd management at the Euclid Oval street activation. Quantity / linear feet to be confirmed by Client; price held as a placeholder pending that confirmation.</t>
+          <t>Branded stanchion poles + ropes for crowd management at the Lincoln Road Mall street activation. Quantity / linear feet to be confirmed by Client; price held as a placeholder pending that confirmation.</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
@@ -988,7 +988,7 @@
     <row r="36" ht="24" customHeight="1">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Phase 04a  —  The Activation (Euclid Oval, 11 AM–8 PM)</t>
+          <t>Phase 04a  —  The Activation (Lincoln Road Mall, 11 AM–8 PM)</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Complete de-installation, module breakdown, crated outbound freight within Euclid Oval's contracted strike window. Site walk-through with the Lincoln Road BID operations team.</t>
+          <t>Complete de-installation, module breakdown, crated outbound freight within the Lincoln Road BID's contracted strike window. Site walk-through with the BID operations team.</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
@@ -1040,7 +1040,7 @@
     <row r="40" ht="22" customHeight="1">
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Subtotal — The Activation (Euclid Oval)</t>
+          <t>Subtotal — The Activation (Lincoln Road Mall)</t>
         </is>
       </c>
       <c r="D40" s="11" t="n">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Venue: Euclid Oval, Lincoln Road Mall</t>
+          <t>Venue: Lincoln Road Mall</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
     <row r="12" ht="70" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Single-event programme: fully-painted pink British phone box with interactive call/voucher/photo tech, deployed for a one-day street activation at Euclid Oval, Lincoln Road Mall, Miami Beach on Friday, July 17, 2026 (Saturday, July 18 held as a weather contingency). Light touchup post-Miami; logistical return to NYC handoff destination — no NYC retail activation, no respray/rewrap package.</t>
+          <t>Single-event programme: fully-painted pink British phone box with interactive call/voucher/photo tech, deployed for a one-day street activation at Lincoln Road Mall, Miami Beach on Friday, July 17, 2026 (Saturday, July 18 held as a weather contingency). Light touchup post-Miami; logistical return to NYC handoff destination — no NYC retail activation, no respray/rewrap package.</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Portable A-frame signage, branded stanchions, pavement decals for the Euclid Oval street activation</t>
+          <t>Portable A-frame signage, branded stanchions, pavement decals for the Lincoln Road Mall street activation</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
@@ -1727,7 +1727,7 @@
     <row r="36" ht="24" customHeight="1">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Phase 04a  —  The Activation (Euclid Oval, Lincoln Road Mall, Miami Beach)</t>
+          <t>Phase 04a  —  The Activation (Lincoln Road Mall, Miami Beach)</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
     <row r="40" ht="22" customHeight="1">
       <c r="B40" s="10" t="inlineStr">
         <is>
-          <t>Subtotal — The Activation (Euclid Oval)</t>
+          <t>Subtotal — The Activation (Lincoln Road Mall)</t>
         </is>
       </c>
       <c r="D40" s="11" t="n">
@@ -2108,7 +2108,7 @@
     <row r="12" ht="70" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Two-event sequence. Event 01 — Miami: Lincoln Road Mall street activation on Saturday, June 27, 2026 (AGV Miami recommended Euclid Oval, 1100 block). Event 02 — New York: in-store fixture at Gymshark Bond St, delivered by July 9, 2026 to anchor the July 11 product launch and a 4-week in-store run through August 6, 2026. Inter-city respray/rewrap to NYC palette between events. [Superseded by V3.0 — included for reference only.]</t>
+          <t>Two-event sequence. Event 01 — Miami: Lincoln Road Mall street activation on Saturday, June 27, 2026 . Event 02 — New York: in-store fixture at Gymshark Bond St, delivered by July 9, 2026 to anchor the July 11 product launch and a 4-week in-store run through August 6, 2026. Inter-city respray/rewrap to NYC palette between events. [Superseded by V3.0 — included for reference only.]</t>
         </is>
       </c>
     </row>

--- a/public/invoices/GS-PHONEBOX-001-V4.0.xlsx
+++ b/public/invoices/GS-PHONEBOX-001-V4.0.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Issue Date: May 7, 2026</t>
+          <t>Issue Date: May 8, 2026</t>
         </is>
       </c>
     </row>
@@ -687,17 +687,17 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="126" customHeight="1">
+    <row r="12" ht="112" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>V4.0 — Yellow palette confirmed; concealed motorised slot replaced with a true hinged back distribution door; tech package itemised against deck spec (2× Motorola RMU2040 radios, 2× Ring Mini Indoor cameras restored to dual per Ominto deck p.15, 80mm thermal voucher printer, 2× wall-mounted selfie stations); content capture omitted; disclosure &amp; wayfinding signage removed; venue dressing kit pared to stanchions only (qty TBC); 200-unit yellow-palette product packaging held; NYC base scope is transport-only with a local install team available as an add-on. $5K Preferred Partner Credit retained. Booth dimensions per Ominto V2 design: 164 × 94 × 213 cm body + 20 cm lightbox header. Activation: Friday, July 17, 2026, 11 AM–8 PM at Lincoln Road Mall (Saturday, July 18 held as a weather contingency).</t>
+          <t>Single-event programme: a fully-painted yellow British phone box equipped with interactive photo, voucher, and call-response technology, deployed for a one-day street activation at Lincoln Road Mall, Miami Beach on Friday, July 17, 2026, 11 AM–8 PM (Saturday, July 18 held as a weather contingency). After Miami the booth ships to AGV Miami's NY shop for a light touchup and is white-glove delivered to the Gymshark NYC flagship store by Thursday, July 23, 2026. Booth dimensions per Ominto V2 design: 164 × 94 cm body + 20 cm lightbox header. Hinged back distribution door for in-booth staff to dispense product directly. $5,000 Preferred Partner Credit applied. Local NYC install team available as an optional add-on.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Phase 01  —  The Phone Box (Painted Yellow, Hinged Back Door)</t>
+          <t>Phase 01  —  The Phone Box</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Custom scenic fabrication per Ominto V2 design pack. Footprint 164 × 94 cm (~5'4" × 3'1"); body height 213 cm (~7'0"); lightbox header +20 cm (total ≈7'8"). Two-piece modular construction (staff compartment 70 cm deep + guest compartment 94 cm deep). Marine-grade paint in Miami yellow (PMS TBC by Ominto).</t>
+          <t>Custom scenic fabrication per Ominto V2 design pack. Footprint 164 × 94 cm (~5'4" × 3'1"); body height 213 cm (~7'0"); lightbox header +20 cm (total ≈7'8"). Two-piece modular construction (staff compartment 70 cm deep + guest compartment 94 cm deep). Marine-grade paint in Miami yellow per Ominto brand guidelines.</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
@@ -764,12 +764,12 @@
     <row r="19" ht="36" customHeight="1">
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Hinged Back Distribution Door (V4 — replaces motorised slot)</t>
+          <t>Hinged Back Distribution Door</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>True hinged back door, brand-yellow painted, no visible handle on the public face. Allows a Gymshark-supplied staff member to operate from inside the back-of-house compartment and hand product directly to the guest. Replaces the previously quoted concealed motorised sliding slot — simpler, lower-cost, and clearer staff workflow.</t>
+          <t>True hinged back door, brand-yellow painted, no visible handle on the public face. Allows a Gymshark-supplied staff member to operate from inside the back-of-house compartment and hand product directly to the guest.</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
@@ -834,7 +834,7 @@
     <row r="24" ht="24" customHeight="1">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Phase 02  —  Interactive Tech (V4 — itemised hardware)</t>
+          <t>Phase 02  —  Interactive Tech</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
     <row r="26" ht="36" customHeight="1">
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Two-Way Radio Pair — Motorola RMU2040 (2 × $350)</t>
+          <t>Two-Way Radio Pair — Motorola RMU2040</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -871,12 +871,12 @@
     <row r="27" ht="36" customHeight="1">
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Ceiling Cameras — Ring Mini Indoor Plug-In (2 × $150)</t>
+          <t>Ceiling Cameras — Ring Mini Indoor Plug-In</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>2 × Ring Mini Indoor Security Cameras (1080p HD, two-way talk, motion detection, plug-in / no batteries, Wi-Fi, white finish). Cloud storage via Ring Protect subscription. Ceiling-mounted in front and back compartments. Restored to dual-camera per the original Ominto deck spec (p.15).</t>
+          <t>2 × Ring Mini Indoor Security Cameras (1080p HD, two-way talk, motion detection, plug-in / no batteries, Wi-Fi, white finish). Cloud storage via Ring Protect subscription. Ceiling-mounted in front and back compartments per Ominto deck spec.</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
@@ -886,12 +886,12 @@
     <row r="28" ht="36" customHeight="1">
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Wall-Mounted Selfie Stations (2 × $450)</t>
+          <t>Wall-Mounted Selfie Stations</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>2 × wall-mounted selfie stations, painted to match the booth interior — face-level + belfie-angle. Each station provides a stable phone holder for guests using their own devices. Replaces V3 mobile-phone-mount line.</t>
+          <t>2 × wall-mounted selfie stations, painted to match the booth interior — face-level + belfie-angle. Each station provides a stable phone holder for guests using their own devices.</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>80mm thermal ticket printer (Amazon-sourced, ~$1,500 hardware-equivalent class), shelf-mounted under the analogue phone, wrapped in yellow vinyl. Voucher template designed by Gymshark; AGV Miami handles printer procurement, firmware, redundant roll inventory.</t>
+          <t>80mm thermal ticket printer, shelf-mounted under the analogue phone, wrapped in yellow vinyl. Voucher template designed by Gymshark; AGV Miami handles printer procurement, firmware, redundant roll inventory.</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
@@ -926,19 +926,19 @@
     <row r="31" ht="24" customHeight="1">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Phase 03  —  Branding, Signage &amp; Consumables (V4 — disclosure removed, dressing pared)</t>
+          <t>Phase 03  —  Branding, Signage &amp; Consumables</t>
         </is>
       </c>
     </row>
     <row r="32" ht="36" customHeight="1">
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Venue Dressing Kit (V4 — stanchions only, qty TBC)</t>
+          <t>Venue Dressing Kit</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Branded stanchion poles + ropes for crowd management at the Lincoln Road Mall street activation. Quantity / linear feet to be confirmed by Client; price held as a placeholder pending that confirmation.</t>
+          <t>Branded stanchion poles and ropes for crowd management at the Lincoln Road Mall street activation. Yellow palette to match booth.</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
@@ -953,7 +953,7 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Voucher paper rolls, cleaning supplies, sanitisation wipes, yellow touch-up paint, vinyl repair, gaffer</t>
+          <t>Voucher paper rolls, cleaning supplies, sanitisation wipes, yellow touch-up paint, vinyl repair, gaffer.</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
@@ -968,7 +968,7 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Yellow-palette product boxes, structural board, full-colour offset print, 300 × 200 × 70 mm, flat-packed for load-in. Held at 200 units per Client direction.</t>
+          <t>Yellow-palette product boxes, structural board, full-colour offset print, 300 × 200 × 70 mm, flat-packed for load-in.</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
@@ -1010,12 +1010,12 @@
     <row r="38" ht="36" customHeight="1">
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>On-Site Technicians (Extended to 8 PM)</t>
+          <t>On-Site Technicians</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Dedicated lead technician plus rotating second tech for rush windows and breaks, covering an extended 11 AM–8 PM operating window. Includes pre-open soundcheck and post-close shutdown.</t>
+          <t>Dedicated lead technician plus rotating second tech for rush windows and breaks, covering the 11 AM–8 PM operating window. Includes pre-open soundcheck and post-close shutdown.</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
@@ -1050,7 +1050,7 @@
     <row r="41" ht="24" customHeight="1">
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Phase 04b  —  Logistics to NYC (V4 — Base, transport-only)</t>
+          <t>Phase 04b  —  Logistics to NYC</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Secure climate-controlled storage at the AGV Miami NYC staging facility between Miami strike and NYC delivery. Held at climate spec per Client direction.</t>
+          <t>Secure climate-controlled storage at AGV Miami's NY shop between Miami strike and Gymshark NYC flagship delivery.</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Miami → AGV Miami NYC staging facility with real-time GPS tracking, two-driver rotation, handoff documentation</t>
+          <t>Miami → AGV Miami NY shop with real-time GPS tracking, two-driver rotation, handoff documentation.</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Light cosmetic touchup pass at AGV Miami's NYC shop after Miami strike, prior to flagship delivery. Per Client direction, the booth ships straight to the NY shop and is refreshed locally before final delivery to the flagship store — tightest possible timeline.</t>
+          <t>Light cosmetic touchup pass at AGV Miami's NY shop following Miami strike: scuff/scratch repair, paint colour-match, lightbox edge cleanup, IVR/camera/printer functional re-test.</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Climate-controlled final-mile delivery from AGV Miami NYC staging to the Gymshark NYC flagship retail address. Scheduled overnight or pre-open per store operations.</t>
+          <t>Climate-controlled final-mile delivery from AGV Miami's NY shop to the Gymshark NYC flagship retail address. Scheduled overnight or pre-open per store operations.</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
@@ -1117,7 +1117,7 @@
     <row r="46" ht="22" customHeight="1">
       <c r="B46" s="10" t="inlineStr">
         <is>
-          <t>Subtotal — Logistics to NYC (Base)</t>
+          <t>Subtotal — Logistics to NYC</t>
         </is>
       </c>
       <c r="D46" s="11" t="n">
@@ -1127,19 +1127,19 @@
     <row r="47" ht="24" customHeight="1">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>Phase 05  —  Project Management (V4 — lean engagement)</t>
+          <t>Phase 05  —  Project Management &amp; Client Services</t>
         </is>
       </c>
     </row>
     <row r="48" ht="36" customHeight="1">
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Project Management Fee (V4 — lean)</t>
+          <t>Project Management Fee</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Dedicated senior producer, weekly status reporting (vs daily), milestone tracking, vendor / venue liaison, COI + insurance coordination, post-event reconciliation. Async-first cadence appropriate for a single-event programme.</t>
+          <t>Dedicated senior producer, weekly status reporting, milestone tracking, vendor / venue liaison, COI + insurance coordination, post-event reconciliation. Async-first cadence appropriate for a single-event programme.</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
@@ -1260,7 +1260,7 @@
     <row r="65" ht="32" customHeight="1">
       <c r="B65" s="18" t="inlineStr">
         <is>
-          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  jclarkson@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V4.0 — current proposed (Base $79,550 net; with optional NYC install add-on $83,950 net) and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
+          <t>AGV Miami, LLC  ·  1440 Church St, Bohemia, NY 11716  ·  jclarkson@agvmiami.com  ·  This invoice is issued in connection with proposal GS-PHONEBOX-001 V4.0 — Lincoln Road Mall, Friday, July 17, 2026 and incorporates by reference the executed Master Services Agreement between AGV Miami, LLC and Gymshark Ltd.</t>
         </is>
       </c>
     </row>
